--- a/api-etl-java/atrativos-turisticos.xlsx
+++ b/api-etl-java/atrativos-turisticos.xlsx
@@ -5,16 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9acbaa33c33b352b/Área de Trabalho/SPTECH/2 Semestre/PI/TourTech/Java/Base de Dados/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9acbaa33c33b352b/Área de Trabalho/SPTECH/2 Semestre/PI/TourTech/api-etl-java/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{113284DB-14B9-4CD1-8C2E-782C6CA20FE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="74" documentId="8_{113284DB-14B9-4CD1-8C2E-782C6CA20FE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87E55FE8-0ECB-4D25-A065-F3447A9256D9}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2B36C75D-4E1F-4573-94E9-0900BBF147A5}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{2B36C75D-4E1F-4573-94E9-0900BBF147A5}"/>
   </bookViews>
   <sheets>
-    <sheet name="Atrativos Turisticos" sheetId="1" r:id="rId1"/>
-    <sheet name="Planilha2" sheetId="2" r:id="rId2"/>
+    <sheet name="Atrativos - RJ" sheetId="4" r:id="rId1"/>
+    <sheet name="Turismo por atrativo - Internac" sheetId="2" r:id="rId2"/>
+    <sheet name="Turismo por atrativo - Nacional" sheetId="3" r:id="rId3"/>
+    <sheet name="Atrativos Turisticos - Nacional" sheetId="1" state="hidden" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="76">
   <si>
     <t>nome</t>
   </si>
@@ -151,6 +153,120 @@
   </si>
   <si>
     <t>Estado</t>
+  </si>
+  <si>
+    <t>JAN</t>
+  </si>
+  <si>
+    <t>FEV</t>
+  </si>
+  <si>
+    <t>MAR</t>
+  </si>
+  <si>
+    <t>ABR</t>
+  </si>
+  <si>
+    <t>MAI</t>
+  </si>
+  <si>
+    <t>JUN</t>
+  </si>
+  <si>
+    <t>JUL</t>
+  </si>
+  <si>
+    <t>AGO</t>
+  </si>
+  <si>
+    <t>SET</t>
+  </si>
+  <si>
+    <t>OUT</t>
+  </si>
+  <si>
+    <t>NOV</t>
+  </si>
+  <si>
+    <t>DEZ</t>
+  </si>
+  <si>
+    <t>Atrativo Turístico</t>
+  </si>
+  <si>
+    <t>Categoria Sugerida</t>
+  </si>
+  <si>
+    <t>Copacabana/Leme</t>
+  </si>
+  <si>
+    <t>Ipanema/Leblon</t>
+  </si>
+  <si>
+    <t>Parque / Lazer</t>
+  </si>
+  <si>
+    <t>Vida Noturna / Cultural</t>
+  </si>
+  <si>
+    <t>Praia: Barra</t>
+  </si>
+  <si>
+    <t>Natureza / Lazer</t>
+  </si>
+  <si>
+    <t>Esporte / Entretenimento</t>
+  </si>
+  <si>
+    <t>Natureza / Científico</t>
+  </si>
+  <si>
+    <t>Religioso / Arquitetura</t>
+  </si>
+  <si>
+    <t>Cultural / Passeio</t>
+  </si>
+  <si>
+    <t>Pequena África</t>
+  </si>
+  <si>
+    <t>Histórico / Cultural</t>
+  </si>
+  <si>
+    <t>Mirante / Natureza</t>
+  </si>
+  <si>
+    <t>Recreio/Macumba</t>
+  </si>
+  <si>
+    <t>Comunidade / Mirante</t>
+  </si>
+  <si>
+    <t>Comunidade / Turismo</t>
+  </si>
+  <si>
+    <t>Cultural / Monumento</t>
+  </si>
+  <si>
+    <t>Tradições Nordestinas</t>
+  </si>
+  <si>
+    <t>Cultural / Gastronomia</t>
+  </si>
+  <si>
+    <t>Monumento / Religioso</t>
+  </si>
+  <si>
+    <t>Cultural / Exposição</t>
+  </si>
+  <si>
+    <t>Natureza / Ecoturismo</t>
+  </si>
+  <si>
+    <t>Munícipio</t>
+  </si>
+  <si>
+    <t>Id</t>
   </si>
 </sst>
 </file>
@@ -186,8 +302,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -521,8 +638,2254 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{624ECD17-AD6A-4DAB-9E83-9865F2D74CB5}">
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
+        <v>58</v>
+      </c>
+      <c r="D8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" t="s">
+        <v>63</v>
+      </c>
+      <c r="D12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" t="s">
+        <v>64</v>
+      </c>
+      <c r="D13" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" t="s">
+        <v>35</v>
+      </c>
+      <c r="E15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" t="s">
+        <v>67</v>
+      </c>
+      <c r="D16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E17" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" t="s">
+        <v>70</v>
+      </c>
+      <c r="D18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" t="s">
+        <v>71</v>
+      </c>
+      <c r="D19" t="s">
+        <v>35</v>
+      </c>
+      <c r="E19" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" t="s">
+        <v>72</v>
+      </c>
+      <c r="D20" t="s">
+        <v>35</v>
+      </c>
+      <c r="E20" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" t="s">
+        <v>73</v>
+      </c>
+      <c r="D21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E21" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73C37A12-E6F8-4DDA-A21F-87BDE073DC18}">
+  <dimension ref="A1:N21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="26.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K1" t="s">
+        <v>46</v>
+      </c>
+      <c r="L1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" s="1">
+        <v>84421</v>
+      </c>
+      <c r="D2" s="1">
+        <v>132295</v>
+      </c>
+      <c r="E2" s="1">
+        <v>118966</v>
+      </c>
+      <c r="F2" s="1">
+        <v>55501</v>
+      </c>
+      <c r="G2" s="1">
+        <v>46173</v>
+      </c>
+      <c r="H2" s="1">
+        <v>42942</v>
+      </c>
+      <c r="I2" s="1">
+        <v>50113</v>
+      </c>
+      <c r="J2" s="1">
+        <v>56470</v>
+      </c>
+      <c r="K2" s="1">
+        <v>66699</v>
+      </c>
+      <c r="L2" s="1">
+        <v>81877</v>
+      </c>
+      <c r="M2" s="1">
+        <v>84733</v>
+      </c>
+      <c r="N2" s="1">
+        <v>105253</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="1">
+        <v>35743</v>
+      </c>
+      <c r="D3" s="1">
+        <v>70903</v>
+      </c>
+      <c r="E3" s="1">
+        <v>67824</v>
+      </c>
+      <c r="F3" s="1">
+        <v>31655</v>
+      </c>
+      <c r="G3" s="1">
+        <v>28062</v>
+      </c>
+      <c r="H3" s="1">
+        <v>27957</v>
+      </c>
+      <c r="I3" s="1">
+        <v>34165</v>
+      </c>
+      <c r="J3" s="1">
+        <v>38258</v>
+      </c>
+      <c r="K3" s="1">
+        <v>43388</v>
+      </c>
+      <c r="L3" s="1">
+        <v>52899</v>
+      </c>
+      <c r="M3" s="1">
+        <v>54216</v>
+      </c>
+      <c r="N3" s="1">
+        <v>69316</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="1">
+        <v>22949</v>
+      </c>
+      <c r="D4" s="1">
+        <v>46547</v>
+      </c>
+      <c r="E4" s="1">
+        <v>38526</v>
+      </c>
+      <c r="F4" s="1">
+        <v>17759</v>
+      </c>
+      <c r="G4" s="1">
+        <v>15243</v>
+      </c>
+      <c r="H4" s="1">
+        <v>14130</v>
+      </c>
+      <c r="I4" s="1">
+        <v>17083</v>
+      </c>
+      <c r="J4" s="1">
+        <v>19316</v>
+      </c>
+      <c r="K4" s="1">
+        <v>23818</v>
+      </c>
+      <c r="L4" s="1">
+        <v>26547</v>
+      </c>
+      <c r="M4" s="1">
+        <v>27138</v>
+      </c>
+      <c r="N4" s="1">
+        <v>32199</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="1">
+        <v>17441</v>
+      </c>
+      <c r="D5" s="1">
+        <v>33823</v>
+      </c>
+      <c r="E5" s="1">
+        <v>30624</v>
+      </c>
+      <c r="F5" s="1">
+        <v>14270</v>
+      </c>
+      <c r="G5" s="1">
+        <v>12531</v>
+      </c>
+      <c r="H5" s="1">
+        <v>12631</v>
+      </c>
+      <c r="I5" s="1">
+        <v>16875</v>
+      </c>
+      <c r="J5" s="1">
+        <v>17898</v>
+      </c>
+      <c r="K5" s="1">
+        <v>19136</v>
+      </c>
+      <c r="L5" s="1">
+        <v>24314</v>
+      </c>
+      <c r="M5" s="1">
+        <v>23676</v>
+      </c>
+      <c r="N5" s="1">
+        <v>29971</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="1">
+        <v>22884</v>
+      </c>
+      <c r="D6" s="1">
+        <v>33207</v>
+      </c>
+      <c r="E6" s="1">
+        <v>28532</v>
+      </c>
+      <c r="F6" s="1">
+        <v>11776</v>
+      </c>
+      <c r="G6" s="1">
+        <v>9791</v>
+      </c>
+      <c r="H6" s="1">
+        <v>8460</v>
+      </c>
+      <c r="I6" s="1">
+        <v>12047</v>
+      </c>
+      <c r="J6" s="1">
+        <v>11824</v>
+      </c>
+      <c r="K6" s="1">
+        <v>14322</v>
+      </c>
+      <c r="L6" s="1">
+        <v>18765</v>
+      </c>
+      <c r="M6" s="1">
+        <v>18182</v>
+      </c>
+      <c r="N6" s="1">
+        <v>24362</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2928</v>
+      </c>
+      <c r="D7" s="1">
+        <v>25572</v>
+      </c>
+      <c r="E7" s="1">
+        <v>25695</v>
+      </c>
+      <c r="F7" s="1">
+        <v>12182</v>
+      </c>
+      <c r="G7" s="1">
+        <v>10391</v>
+      </c>
+      <c r="H7" s="1">
+        <v>10321</v>
+      </c>
+      <c r="I7" s="1">
+        <v>13664</v>
+      </c>
+      <c r="J7" s="1">
+        <v>16868</v>
+      </c>
+      <c r="K7" s="1">
+        <v>18507</v>
+      </c>
+      <c r="L7" s="1">
+        <v>22810</v>
+      </c>
+      <c r="M7" s="1">
+        <v>21905</v>
+      </c>
+      <c r="N7" s="1">
+        <v>25502</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="1">
+        <v>12952</v>
+      </c>
+      <c r="D8" s="1">
+        <v>29092</v>
+      </c>
+      <c r="E8" s="1">
+        <v>23732</v>
+      </c>
+      <c r="F8" s="1">
+        <v>10599</v>
+      </c>
+      <c r="G8" s="1">
+        <v>8450</v>
+      </c>
+      <c r="H8" s="1">
+        <v>8186</v>
+      </c>
+      <c r="I8" s="1">
+        <v>10038</v>
+      </c>
+      <c r="J8" s="1">
+        <v>11996</v>
+      </c>
+      <c r="K8" s="1">
+        <v>14777</v>
+      </c>
+      <c r="L8" s="1">
+        <v>18221</v>
+      </c>
+      <c r="M8" s="1">
+        <v>18334</v>
+      </c>
+      <c r="N8" s="1">
+        <v>20433</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="1">
+        <v>19996</v>
+      </c>
+      <c r="D9" s="1">
+        <v>27964</v>
+      </c>
+      <c r="E9" s="1">
+        <v>27444</v>
+      </c>
+      <c r="F9" s="1">
+        <v>8879</v>
+      </c>
+      <c r="G9" s="1">
+        <v>4766</v>
+      </c>
+      <c r="H9" s="1">
+        <v>3890</v>
+      </c>
+      <c r="I9" s="1">
+        <v>5502</v>
+      </c>
+      <c r="J9" s="1">
+        <v>5771</v>
+      </c>
+      <c r="K9" s="1">
+        <v>8724</v>
+      </c>
+      <c r="L9" s="1">
+        <v>10465</v>
+      </c>
+      <c r="M9" s="1">
+        <v>11795</v>
+      </c>
+      <c r="N9" s="1">
+        <v>20336</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="1">
+        <v>4353</v>
+      </c>
+      <c r="D10" s="1">
+        <v>16058</v>
+      </c>
+      <c r="E10" s="1">
+        <v>14046</v>
+      </c>
+      <c r="F10" s="1">
+        <v>8368</v>
+      </c>
+      <c r="G10" s="1">
+        <v>6683</v>
+      </c>
+      <c r="H10" s="1">
+        <v>6029</v>
+      </c>
+      <c r="I10" s="1">
+        <v>7417</v>
+      </c>
+      <c r="J10" s="1">
+        <v>7928</v>
+      </c>
+      <c r="K10" s="1">
+        <v>10146</v>
+      </c>
+      <c r="L10" s="1">
+        <v>10618</v>
+      </c>
+      <c r="M10" s="1">
+        <v>10217</v>
+      </c>
+      <c r="N10" s="1">
+        <v>11076</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" s="1">
+        <v>13813</v>
+      </c>
+      <c r="D11" s="1">
+        <v>18186</v>
+      </c>
+      <c r="E11" s="1">
+        <v>17999</v>
+      </c>
+      <c r="F11" s="1">
+        <v>6229</v>
+      </c>
+      <c r="G11" s="1">
+        <v>3204</v>
+      </c>
+      <c r="H11" s="1">
+        <v>2404</v>
+      </c>
+      <c r="I11" s="1">
+        <v>3534</v>
+      </c>
+      <c r="J11" s="1">
+        <v>4100</v>
+      </c>
+      <c r="K11" s="1">
+        <v>6610</v>
+      </c>
+      <c r="L11" s="1">
+        <v>6770</v>
+      </c>
+      <c r="M11" s="1">
+        <v>7279</v>
+      </c>
+      <c r="N11" s="1">
+        <v>13754</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="1">
+        <v>6152</v>
+      </c>
+      <c r="D12" s="1">
+        <v>13797</v>
+      </c>
+      <c r="E12" s="1">
+        <v>11189</v>
+      </c>
+      <c r="F12" s="1">
+        <v>4649</v>
+      </c>
+      <c r="G12" s="1">
+        <v>3820</v>
+      </c>
+      <c r="H12" s="1">
+        <v>3712</v>
+      </c>
+      <c r="I12" s="1">
+        <v>4336</v>
+      </c>
+      <c r="J12" s="1">
+        <v>5558</v>
+      </c>
+      <c r="K12" s="1">
+        <v>6725</v>
+      </c>
+      <c r="L12" s="1">
+        <v>8145</v>
+      </c>
+      <c r="M12" s="1">
+        <v>8610</v>
+      </c>
+      <c r="N12" s="1">
+        <v>9531</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="1">
+        <v>5244</v>
+      </c>
+      <c r="D13" s="1">
+        <v>10975</v>
+      </c>
+      <c r="E13" s="1">
+        <v>9792</v>
+      </c>
+      <c r="F13" s="1">
+        <v>5153</v>
+      </c>
+      <c r="G13" s="1">
+        <v>4531</v>
+      </c>
+      <c r="H13" s="1">
+        <v>4304</v>
+      </c>
+      <c r="I13" s="1">
+        <v>4957</v>
+      </c>
+      <c r="J13" s="1">
+        <v>5326</v>
+      </c>
+      <c r="K13" s="1">
+        <v>6221</v>
+      </c>
+      <c r="L13" s="1">
+        <v>7064</v>
+      </c>
+      <c r="M13" s="1">
+        <v>7677</v>
+      </c>
+      <c r="N13" s="1">
+        <v>10388</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="1">
+        <v>3504</v>
+      </c>
+      <c r="D14" s="1">
+        <v>6587</v>
+      </c>
+      <c r="E14" s="1">
+        <v>5862</v>
+      </c>
+      <c r="F14" s="1">
+        <v>2924</v>
+      </c>
+      <c r="G14" s="1">
+        <v>2624</v>
+      </c>
+      <c r="H14" s="1">
+        <v>2822</v>
+      </c>
+      <c r="I14" s="1">
+        <v>4094</v>
+      </c>
+      <c r="J14" s="1">
+        <v>4257</v>
+      </c>
+      <c r="K14" s="1">
+        <v>4357</v>
+      </c>
+      <c r="L14" s="1">
+        <v>5914</v>
+      </c>
+      <c r="M14" s="1">
+        <v>5571</v>
+      </c>
+      <c r="N14" s="1">
+        <v>6946</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>65</v>
+      </c>
+      <c r="C15" s="1">
+        <v>5429</v>
+      </c>
+      <c r="D15" s="1">
+        <v>6911</v>
+      </c>
+      <c r="E15" s="1">
+        <v>5078</v>
+      </c>
+      <c r="F15" s="1">
+        <v>2513</v>
+      </c>
+      <c r="G15" s="1">
+        <v>1932</v>
+      </c>
+      <c r="H15" s="1">
+        <v>2216</v>
+      </c>
+      <c r="I15" s="1">
+        <v>2962</v>
+      </c>
+      <c r="J15" s="1">
+        <v>2925</v>
+      </c>
+      <c r="K15" s="1">
+        <v>3483</v>
+      </c>
+      <c r="L15" s="1">
+        <v>3206</v>
+      </c>
+      <c r="M15" s="1">
+        <v>3731</v>
+      </c>
+      <c r="N15" s="1">
+        <v>5547</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="1">
+        <v>3136</v>
+      </c>
+      <c r="D16" s="1">
+        <v>5681</v>
+      </c>
+      <c r="E16" s="1">
+        <v>5068</v>
+      </c>
+      <c r="F16" s="1">
+        <v>2330</v>
+      </c>
+      <c r="G16" s="1">
+        <v>2149</v>
+      </c>
+      <c r="H16" s="1">
+        <v>2111</v>
+      </c>
+      <c r="I16" s="1">
+        <v>2889</v>
+      </c>
+      <c r="J16" s="1">
+        <v>3736</v>
+      </c>
+      <c r="K16" s="1">
+        <v>3632</v>
+      </c>
+      <c r="L16" s="1">
+        <v>4556</v>
+      </c>
+      <c r="M16" s="1">
+        <v>4649</v>
+      </c>
+      <c r="N16" s="1">
+        <v>5707</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="1">
+        <v>4094</v>
+      </c>
+      <c r="D17" s="1">
+        <v>6508</v>
+      </c>
+      <c r="E17" s="1">
+        <v>5275</v>
+      </c>
+      <c r="F17" s="1">
+        <v>2086</v>
+      </c>
+      <c r="G17" s="1">
+        <v>1665</v>
+      </c>
+      <c r="H17" s="1">
+        <v>1488</v>
+      </c>
+      <c r="I17" s="1">
+        <v>2163</v>
+      </c>
+      <c r="J17" s="1">
+        <v>2399</v>
+      </c>
+      <c r="K17" s="1">
+        <v>2620</v>
+      </c>
+      <c r="L17" s="1">
+        <v>3797</v>
+      </c>
+      <c r="M17" s="1">
+        <v>3733</v>
+      </c>
+      <c r="N17" s="1">
+        <v>5012</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="1">
+        <v>1462</v>
+      </c>
+      <c r="D18" s="1">
+        <v>3487</v>
+      </c>
+      <c r="E18" s="1">
+        <v>2164</v>
+      </c>
+      <c r="F18">
+        <v>872</v>
+      </c>
+      <c r="G18">
+        <v>824</v>
+      </c>
+      <c r="H18">
+        <v>742</v>
+      </c>
+      <c r="I18">
+        <v>867</v>
+      </c>
+      <c r="J18" s="1">
+        <v>1032</v>
+      </c>
+      <c r="K18" s="1">
+        <v>1357</v>
+      </c>
+      <c r="L18" s="1">
+        <v>1548</v>
+      </c>
+      <c r="M18" s="1">
+        <v>1760</v>
+      </c>
+      <c r="N18" s="1">
+        <v>2136</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19">
+        <v>633</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1558</v>
+      </c>
+      <c r="E19" s="1">
+        <v>1151</v>
+      </c>
+      <c r="F19">
+        <v>405</v>
+      </c>
+      <c r="G19">
+        <v>336</v>
+      </c>
+      <c r="H19">
+        <v>496</v>
+      </c>
+      <c r="I19">
+        <v>597</v>
+      </c>
+      <c r="J19">
+        <v>632</v>
+      </c>
+      <c r="K19">
+        <v>555</v>
+      </c>
+      <c r="L19">
+        <v>704</v>
+      </c>
+      <c r="M19">
+        <v>717</v>
+      </c>
+      <c r="N19">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20">
+        <v>674</v>
+      </c>
+      <c r="D20">
+        <v>913</v>
+      </c>
+      <c r="E20">
+        <v>851</v>
+      </c>
+      <c r="F20">
+        <v>361</v>
+      </c>
+      <c r="G20">
+        <v>249</v>
+      </c>
+      <c r="H20">
+        <v>271</v>
+      </c>
+      <c r="I20">
+        <v>599</v>
+      </c>
+      <c r="J20">
+        <v>708</v>
+      </c>
+      <c r="K20">
+        <v>661</v>
+      </c>
+      <c r="L20">
+        <v>722</v>
+      </c>
+      <c r="M20">
+        <v>685</v>
+      </c>
+      <c r="N20">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21">
+        <v>249</v>
+      </c>
+      <c r="D21">
+        <v>648</v>
+      </c>
+      <c r="E21">
+        <v>650</v>
+      </c>
+      <c r="F21">
+        <v>265</v>
+      </c>
+      <c r="G21">
+        <v>370</v>
+      </c>
+      <c r="H21">
+        <v>224</v>
+      </c>
+      <c r="I21">
+        <v>287</v>
+      </c>
+      <c r="J21">
+        <v>312</v>
+      </c>
+      <c r="K21">
+        <v>355</v>
+      </c>
+      <c r="L21">
+        <v>427</v>
+      </c>
+      <c r="M21">
+        <v>418</v>
+      </c>
+      <c r="N21">
+        <v>609</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE40524E-1ADE-437F-AACF-553CE8D3F25F}">
+  <dimension ref="A1:N21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K1" t="s">
+        <v>46</v>
+      </c>
+      <c r="L1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" s="1">
+        <v>259459</v>
+      </c>
+      <c r="D2" s="1">
+        <v>196767</v>
+      </c>
+      <c r="E2" s="1">
+        <v>167231</v>
+      </c>
+      <c r="F2" s="1">
+        <v>166852</v>
+      </c>
+      <c r="G2" s="1">
+        <v>241733</v>
+      </c>
+      <c r="H2" s="1">
+        <v>187870</v>
+      </c>
+      <c r="I2" s="1">
+        <v>220226</v>
+      </c>
+      <c r="J2" s="1">
+        <v>206200</v>
+      </c>
+      <c r="K2" s="1">
+        <v>287734</v>
+      </c>
+      <c r="L2" s="1">
+        <v>224876</v>
+      </c>
+      <c r="M2" s="1">
+        <v>252059</v>
+      </c>
+      <c r="N2" s="1">
+        <v>276665</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="1">
+        <v>177217</v>
+      </c>
+      <c r="D3" s="1">
+        <v>165274</v>
+      </c>
+      <c r="E3" s="1">
+        <v>115487</v>
+      </c>
+      <c r="F3" s="1">
+        <v>114875</v>
+      </c>
+      <c r="G3" s="1">
+        <v>153407</v>
+      </c>
+      <c r="H3" s="1">
+        <v>139907</v>
+      </c>
+      <c r="I3" s="1">
+        <v>155614</v>
+      </c>
+      <c r="J3" s="1">
+        <v>145675</v>
+      </c>
+      <c r="K3" s="1">
+        <v>218664</v>
+      </c>
+      <c r="L3" s="1">
+        <v>157837</v>
+      </c>
+      <c r="M3" s="1">
+        <v>190559</v>
+      </c>
+      <c r="N3" s="1">
+        <v>225931</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="1">
+        <v>168962</v>
+      </c>
+      <c r="D4" s="1">
+        <v>161845</v>
+      </c>
+      <c r="E4" s="1">
+        <v>119488</v>
+      </c>
+      <c r="F4" s="1">
+        <v>115628</v>
+      </c>
+      <c r="G4" s="1">
+        <v>139347</v>
+      </c>
+      <c r="H4" s="1">
+        <v>137742</v>
+      </c>
+      <c r="I4" s="1">
+        <v>151557</v>
+      </c>
+      <c r="J4" s="1">
+        <v>156673</v>
+      </c>
+      <c r="K4" s="1">
+        <v>179888</v>
+      </c>
+      <c r="L4" s="1">
+        <v>152124</v>
+      </c>
+      <c r="M4" s="1">
+        <v>162913</v>
+      </c>
+      <c r="N4" s="1">
+        <v>186604</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="1">
+        <v>94929</v>
+      </c>
+      <c r="D5" s="1">
+        <v>91388</v>
+      </c>
+      <c r="E5" s="1">
+        <v>65863</v>
+      </c>
+      <c r="F5" s="1">
+        <v>66663</v>
+      </c>
+      <c r="G5" s="1">
+        <v>79857</v>
+      </c>
+      <c r="H5" s="1">
+        <v>68822</v>
+      </c>
+      <c r="I5" s="1">
+        <v>82794</v>
+      </c>
+      <c r="J5" s="1">
+        <v>86097</v>
+      </c>
+      <c r="K5" s="1">
+        <v>105721</v>
+      </c>
+      <c r="L5" s="1">
+        <v>90705</v>
+      </c>
+      <c r="M5" s="1">
+        <v>108961</v>
+      </c>
+      <c r="N5" s="1">
+        <v>100902</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="1">
+        <v>103924</v>
+      </c>
+      <c r="D6" s="1">
+        <v>80475</v>
+      </c>
+      <c r="E6" s="1">
+        <v>68942</v>
+      </c>
+      <c r="F6" s="1">
+        <v>64162</v>
+      </c>
+      <c r="G6" s="1">
+        <v>69450</v>
+      </c>
+      <c r="H6" s="1">
+        <v>68489</v>
+      </c>
+      <c r="I6" s="1">
+        <v>74747</v>
+      </c>
+      <c r="J6" s="1">
+        <v>77322</v>
+      </c>
+      <c r="K6" s="1">
+        <v>106801</v>
+      </c>
+      <c r="L6" s="1">
+        <v>78327</v>
+      </c>
+      <c r="M6" s="1">
+        <v>88445</v>
+      </c>
+      <c r="N6" s="1">
+        <v>119318</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="1">
+        <v>94715</v>
+      </c>
+      <c r="D7" s="1">
+        <v>84463</v>
+      </c>
+      <c r="E7" s="1">
+        <v>55413</v>
+      </c>
+      <c r="F7" s="1">
+        <v>57175</v>
+      </c>
+      <c r="G7" s="1">
+        <v>70832</v>
+      </c>
+      <c r="H7" s="1">
+        <v>64714</v>
+      </c>
+      <c r="I7" s="1">
+        <v>84952</v>
+      </c>
+      <c r="J7" s="1">
+        <v>72369</v>
+      </c>
+      <c r="K7" s="1">
+        <v>95417</v>
+      </c>
+      <c r="L7" s="1">
+        <v>77751</v>
+      </c>
+      <c r="M7" s="1">
+        <v>88094</v>
+      </c>
+      <c r="N7" s="1">
+        <v>99081</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="1">
+        <v>48919</v>
+      </c>
+      <c r="D8" s="1">
+        <v>58777</v>
+      </c>
+      <c r="E8" s="1">
+        <v>49009</v>
+      </c>
+      <c r="F8" s="1">
+        <v>51745</v>
+      </c>
+      <c r="G8" s="1">
+        <v>65799</v>
+      </c>
+      <c r="H8" s="1">
+        <v>56947</v>
+      </c>
+      <c r="I8" s="1">
+        <v>72607</v>
+      </c>
+      <c r="J8" s="1">
+        <v>70353</v>
+      </c>
+      <c r="K8" s="1">
+        <v>72215</v>
+      </c>
+      <c r="L8" s="1">
+        <v>65058</v>
+      </c>
+      <c r="M8" s="1">
+        <v>72531</v>
+      </c>
+      <c r="N8" s="1">
+        <v>66599</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="1">
+        <v>68747</v>
+      </c>
+      <c r="D9" s="1">
+        <v>60014</v>
+      </c>
+      <c r="E9" s="1">
+        <v>41980</v>
+      </c>
+      <c r="F9" s="1">
+        <v>43343</v>
+      </c>
+      <c r="G9" s="1">
+        <v>54552</v>
+      </c>
+      <c r="H9" s="1">
+        <v>47014</v>
+      </c>
+      <c r="I9" s="1">
+        <v>65461</v>
+      </c>
+      <c r="J9" s="1">
+        <v>52078</v>
+      </c>
+      <c r="K9" s="1">
+        <v>63336</v>
+      </c>
+      <c r="L9" s="1">
+        <v>55730</v>
+      </c>
+      <c r="M9" s="1">
+        <v>62926</v>
+      </c>
+      <c r="N9" s="1">
+        <v>73249</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="1">
+        <v>57001</v>
+      </c>
+      <c r="D10" s="1">
+        <v>49194</v>
+      </c>
+      <c r="E10" s="1">
+        <v>40509</v>
+      </c>
+      <c r="F10" s="1">
+        <v>39795</v>
+      </c>
+      <c r="G10" s="1">
+        <v>47234</v>
+      </c>
+      <c r="H10" s="1">
+        <v>39961</v>
+      </c>
+      <c r="I10" s="1">
+        <v>48244</v>
+      </c>
+      <c r="J10" s="1">
+        <v>51388</v>
+      </c>
+      <c r="K10" s="1">
+        <v>61805</v>
+      </c>
+      <c r="L10" s="1">
+        <v>55705</v>
+      </c>
+      <c r="M10" s="1">
+        <v>68602</v>
+      </c>
+      <c r="N10" s="1">
+        <v>56680</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="1">
+        <v>59555</v>
+      </c>
+      <c r="D11" s="1">
+        <v>60765</v>
+      </c>
+      <c r="E11" s="1">
+        <v>51454</v>
+      </c>
+      <c r="F11" s="1">
+        <v>37486</v>
+      </c>
+      <c r="G11" s="1">
+        <v>32561</v>
+      </c>
+      <c r="H11" s="1">
+        <v>26061</v>
+      </c>
+      <c r="I11" s="1">
+        <v>43745</v>
+      </c>
+      <c r="J11" s="1">
+        <v>36543</v>
+      </c>
+      <c r="K11" s="1">
+        <v>56910</v>
+      </c>
+      <c r="L11" s="1">
+        <v>39234</v>
+      </c>
+      <c r="M11" s="1">
+        <v>56856</v>
+      </c>
+      <c r="N11" s="1">
+        <v>63582</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="1">
+        <v>45453</v>
+      </c>
+      <c r="D12" s="1">
+        <v>52356</v>
+      </c>
+      <c r="E12" s="1">
+        <v>38871</v>
+      </c>
+      <c r="F12" s="1">
+        <v>29961</v>
+      </c>
+      <c r="G12" s="1">
+        <v>26474</v>
+      </c>
+      <c r="H12" s="1">
+        <v>20749</v>
+      </c>
+      <c r="I12" s="1">
+        <v>28643</v>
+      </c>
+      <c r="J12" s="1">
+        <v>28948</v>
+      </c>
+      <c r="K12" s="1">
+        <v>49063</v>
+      </c>
+      <c r="L12" s="1">
+        <v>29540</v>
+      </c>
+      <c r="M12" s="1">
+        <v>47007</v>
+      </c>
+      <c r="N12" s="1">
+        <v>55209</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="1">
+        <v>37359</v>
+      </c>
+      <c r="D13" s="1">
+        <v>25988</v>
+      </c>
+      <c r="E13" s="1">
+        <v>26461</v>
+      </c>
+      <c r="F13" s="1">
+        <v>27929</v>
+      </c>
+      <c r="G13" s="1">
+        <v>31856</v>
+      </c>
+      <c r="H13" s="1">
+        <v>26933</v>
+      </c>
+      <c r="I13" s="1">
+        <v>43174</v>
+      </c>
+      <c r="J13" s="1">
+        <v>35954</v>
+      </c>
+      <c r="K13" s="1">
+        <v>51976</v>
+      </c>
+      <c r="L13" s="1">
+        <v>39378</v>
+      </c>
+      <c r="M13" s="1">
+        <v>41693</v>
+      </c>
+      <c r="N13" s="1">
+        <v>43248</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" s="1">
+        <v>51331</v>
+      </c>
+      <c r="D14" s="1">
+        <v>34924</v>
+      </c>
+      <c r="E14" s="1">
+        <v>25575</v>
+      </c>
+      <c r="F14" s="1">
+        <v>23599</v>
+      </c>
+      <c r="G14" s="1">
+        <v>24557</v>
+      </c>
+      <c r="H14" s="1">
+        <v>21839</v>
+      </c>
+      <c r="I14" s="1">
+        <v>28687</v>
+      </c>
+      <c r="J14" s="1">
+        <v>25827</v>
+      </c>
+      <c r="K14" s="1">
+        <v>42531</v>
+      </c>
+      <c r="L14" s="1">
+        <v>26265</v>
+      </c>
+      <c r="M14" s="1">
+        <v>32778</v>
+      </c>
+      <c r="N14" s="1">
+        <v>54948</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="1">
+        <v>30394</v>
+      </c>
+      <c r="D15" s="1">
+        <v>29015</v>
+      </c>
+      <c r="E15" s="1">
+        <v>20867</v>
+      </c>
+      <c r="F15" s="1">
+        <v>18005</v>
+      </c>
+      <c r="G15" s="1">
+        <v>17834</v>
+      </c>
+      <c r="H15" s="1">
+        <v>17645</v>
+      </c>
+      <c r="I15" s="1">
+        <v>19457</v>
+      </c>
+      <c r="J15" s="1">
+        <v>18201</v>
+      </c>
+      <c r="K15" s="1">
+        <v>22525</v>
+      </c>
+      <c r="L15" s="1">
+        <v>17657</v>
+      </c>
+      <c r="M15" s="1">
+        <v>22404</v>
+      </c>
+      <c r="N15" s="1">
+        <v>32474</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="1">
+        <v>18067</v>
+      </c>
+      <c r="D16" s="1">
+        <v>13980</v>
+      </c>
+      <c r="E16" s="1">
+        <v>11524</v>
+      </c>
+      <c r="F16" s="1">
+        <v>11195</v>
+      </c>
+      <c r="G16" s="1">
+        <v>11292</v>
+      </c>
+      <c r="H16" s="1">
+        <v>11061</v>
+      </c>
+      <c r="I16" s="1">
+        <v>15294</v>
+      </c>
+      <c r="J16" s="1">
+        <v>15256</v>
+      </c>
+      <c r="K16" s="1">
+        <v>14783</v>
+      </c>
+      <c r="L16" s="1">
+        <v>14585</v>
+      </c>
+      <c r="M16" s="1">
+        <v>15672</v>
+      </c>
+      <c r="N16" s="1">
+        <v>19224</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="1">
+        <v>17374</v>
+      </c>
+      <c r="D17" s="1">
+        <v>15783</v>
+      </c>
+      <c r="E17" s="1">
+        <v>10762</v>
+      </c>
+      <c r="F17" s="1">
+        <v>10382</v>
+      </c>
+      <c r="G17" s="1">
+        <v>12129</v>
+      </c>
+      <c r="H17" s="1">
+        <v>10913</v>
+      </c>
+      <c r="I17" s="1">
+        <v>13179</v>
+      </c>
+      <c r="J17" s="1">
+        <v>14472</v>
+      </c>
+      <c r="K17" s="1">
+        <v>17422</v>
+      </c>
+      <c r="L17" s="1">
+        <v>14732</v>
+      </c>
+      <c r="M17" s="1">
+        <v>18262</v>
+      </c>
+      <c r="N17" s="1">
+        <v>15804</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" s="1">
+        <v>12451</v>
+      </c>
+      <c r="D18" s="1">
+        <v>10740</v>
+      </c>
+      <c r="E18" s="1">
+        <v>8434</v>
+      </c>
+      <c r="F18" s="1">
+        <v>7760</v>
+      </c>
+      <c r="G18" s="1">
+        <v>9377</v>
+      </c>
+      <c r="H18" s="1">
+        <v>10764</v>
+      </c>
+      <c r="I18" s="1">
+        <v>13288</v>
+      </c>
+      <c r="J18" s="1">
+        <v>11556</v>
+      </c>
+      <c r="K18" s="1">
+        <v>10279</v>
+      </c>
+      <c r="L18" s="1">
+        <v>12155</v>
+      </c>
+      <c r="M18" s="1">
+        <v>12977</v>
+      </c>
+      <c r="N18" s="1">
+        <v>14092</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" s="1">
+        <v>11240</v>
+      </c>
+      <c r="D19" s="1">
+        <v>7558</v>
+      </c>
+      <c r="E19" s="1">
+        <v>7471</v>
+      </c>
+      <c r="F19" s="1">
+        <v>7587</v>
+      </c>
+      <c r="G19" s="1">
+        <v>7506</v>
+      </c>
+      <c r="H19" s="1">
+        <v>7808</v>
+      </c>
+      <c r="I19" s="1">
+        <v>10398</v>
+      </c>
+      <c r="J19" s="1">
+        <v>9351</v>
+      </c>
+      <c r="K19" s="1">
+        <v>10332</v>
+      </c>
+      <c r="L19" s="1">
+        <v>8758</v>
+      </c>
+      <c r="M19" s="1">
+        <v>9474</v>
+      </c>
+      <c r="N19" s="1">
+        <v>10330</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" s="1">
+        <v>6339</v>
+      </c>
+      <c r="D20" s="1">
+        <v>5447</v>
+      </c>
+      <c r="E20" s="1">
+        <v>4559</v>
+      </c>
+      <c r="F20" s="1">
+        <v>5027</v>
+      </c>
+      <c r="G20" s="1">
+        <v>5009</v>
+      </c>
+      <c r="H20" s="1">
+        <v>5583</v>
+      </c>
+      <c r="I20" s="1">
+        <v>7398</v>
+      </c>
+      <c r="J20" s="1">
+        <v>7201</v>
+      </c>
+      <c r="K20" s="1">
+        <v>6530</v>
+      </c>
+      <c r="L20" s="1">
+        <v>6490</v>
+      </c>
+      <c r="M20" s="1">
+        <v>6159</v>
+      </c>
+      <c r="N20" s="1">
+        <v>5930</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="1">
+        <v>2544</v>
+      </c>
+      <c r="D21" s="1">
+        <v>2004</v>
+      </c>
+      <c r="E21" s="1">
+        <v>1793</v>
+      </c>
+      <c r="F21" s="1">
+        <v>1618</v>
+      </c>
+      <c r="G21" s="1">
+        <v>1813</v>
+      </c>
+      <c r="H21" s="1">
+        <v>1675</v>
+      </c>
+      <c r="I21" s="1">
+        <v>2385</v>
+      </c>
+      <c r="J21" s="1">
+        <v>2048</v>
+      </c>
+      <c r="K21" s="1">
+        <v>2299</v>
+      </c>
+      <c r="L21" s="1">
+        <v>1926</v>
+      </c>
+      <c r="M21" s="1">
+        <v>2300</v>
+      </c>
+      <c r="N21" s="1">
+        <v>2702</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40AE52EE-43C1-44E2-A831-70E11154C831}">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="30.85546875" bestFit="1" customWidth="1"/>
@@ -530,7 +2893,7 @@
     <col min="4" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>34</v>
       </c>
@@ -546,8 +2909,44 @@
       <c r="E1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L1" t="s">
+        <v>44</v>
+      </c>
+      <c r="M1" t="s">
+        <v>45</v>
+      </c>
+      <c r="N1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -563,8 +2962,44 @@
       <c r="E2" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2" s="1">
+        <v>84421</v>
+      </c>
+      <c r="G2" s="1">
+        <v>132295</v>
+      </c>
+      <c r="H2" s="1">
+        <v>118966</v>
+      </c>
+      <c r="I2" s="1">
+        <v>55501</v>
+      </c>
+      <c r="J2" s="1">
+        <v>46173</v>
+      </c>
+      <c r="K2" s="1">
+        <v>42942</v>
+      </c>
+      <c r="L2" s="1">
+        <v>50113</v>
+      </c>
+      <c r="M2" s="1">
+        <v>56470</v>
+      </c>
+      <c r="N2" s="1">
+        <v>66699</v>
+      </c>
+      <c r="O2" s="1">
+        <v>81877</v>
+      </c>
+      <c r="P2" s="1">
+        <v>84733</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>105253</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -580,8 +3015,44 @@
       <c r="E3" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F3" s="1">
+        <v>35743</v>
+      </c>
+      <c r="G3" s="1">
+        <v>70903</v>
+      </c>
+      <c r="H3" s="1">
+        <v>67824</v>
+      </c>
+      <c r="I3" s="1">
+        <v>31655</v>
+      </c>
+      <c r="J3" s="1">
+        <v>28062</v>
+      </c>
+      <c r="K3" s="1">
+        <v>27957</v>
+      </c>
+      <c r="L3" s="1">
+        <v>34165</v>
+      </c>
+      <c r="M3" s="1">
+        <v>38258</v>
+      </c>
+      <c r="N3" s="1">
+        <v>43388</v>
+      </c>
+      <c r="O3" s="1">
+        <v>52899</v>
+      </c>
+      <c r="P3" s="1">
+        <v>54216</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>69316</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -597,8 +3068,44 @@
       <c r="E4" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4" s="1">
+        <v>22949</v>
+      </c>
+      <c r="G4" s="1">
+        <v>46547</v>
+      </c>
+      <c r="H4" s="1">
+        <v>38526</v>
+      </c>
+      <c r="I4" s="1">
+        <v>17759</v>
+      </c>
+      <c r="J4" s="1">
+        <v>15243</v>
+      </c>
+      <c r="K4" s="1">
+        <v>14130</v>
+      </c>
+      <c r="L4" s="1">
+        <v>17083</v>
+      </c>
+      <c r="M4" s="1">
+        <v>19316</v>
+      </c>
+      <c r="N4" s="1">
+        <v>23818</v>
+      </c>
+      <c r="O4" s="1">
+        <v>26547</v>
+      </c>
+      <c r="P4" s="1">
+        <v>27138</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>32199</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -614,8 +3121,44 @@
       <c r="E5" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5" s="1">
+        <v>17441</v>
+      </c>
+      <c r="G5" s="1">
+        <v>33823</v>
+      </c>
+      <c r="H5" s="1">
+        <v>30624</v>
+      </c>
+      <c r="I5" s="1">
+        <v>14270</v>
+      </c>
+      <c r="J5" s="1">
+        <v>12531</v>
+      </c>
+      <c r="K5" s="1">
+        <v>12631</v>
+      </c>
+      <c r="L5" s="1">
+        <v>16875</v>
+      </c>
+      <c r="M5" s="1">
+        <v>17898</v>
+      </c>
+      <c r="N5" s="1">
+        <v>19136</v>
+      </c>
+      <c r="O5" s="1">
+        <v>24314</v>
+      </c>
+      <c r="P5" s="1">
+        <v>23676</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>29971</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -631,8 +3174,44 @@
       <c r="E6" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F6" s="1">
+        <v>22884</v>
+      </c>
+      <c r="G6" s="1">
+        <v>33207</v>
+      </c>
+      <c r="H6" s="1">
+        <v>28532</v>
+      </c>
+      <c r="I6" s="1">
+        <v>11776</v>
+      </c>
+      <c r="J6" s="1">
+        <v>9791</v>
+      </c>
+      <c r="K6" s="1">
+        <v>8460</v>
+      </c>
+      <c r="L6" s="1">
+        <v>12047</v>
+      </c>
+      <c r="M6" s="1">
+        <v>11824</v>
+      </c>
+      <c r="N6" s="1">
+        <v>14322</v>
+      </c>
+      <c r="O6" s="1">
+        <v>18765</v>
+      </c>
+      <c r="P6" s="1">
+        <v>18182</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>24362</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -648,8 +3227,44 @@
       <c r="E7" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F7" s="1">
+        <v>2928</v>
+      </c>
+      <c r="G7" s="1">
+        <v>25572</v>
+      </c>
+      <c r="H7" s="1">
+        <v>25695</v>
+      </c>
+      <c r="I7" s="1">
+        <v>12182</v>
+      </c>
+      <c r="J7" s="1">
+        <v>10391</v>
+      </c>
+      <c r="K7" s="1">
+        <v>10321</v>
+      </c>
+      <c r="L7" s="1">
+        <v>13664</v>
+      </c>
+      <c r="M7" s="1">
+        <v>16868</v>
+      </c>
+      <c r="N7" s="1">
+        <v>18507</v>
+      </c>
+      <c r="O7" s="1">
+        <v>22810</v>
+      </c>
+      <c r="P7" s="1">
+        <v>21905</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>25502</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -665,8 +3280,44 @@
       <c r="E8" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F8" s="1">
+        <v>12952</v>
+      </c>
+      <c r="G8" s="1">
+        <v>29092</v>
+      </c>
+      <c r="H8" s="1">
+        <v>23732</v>
+      </c>
+      <c r="I8" s="1">
+        <v>10599</v>
+      </c>
+      <c r="J8" s="1">
+        <v>8450</v>
+      </c>
+      <c r="K8" s="1">
+        <v>8186</v>
+      </c>
+      <c r="L8" s="1">
+        <v>10038</v>
+      </c>
+      <c r="M8" s="1">
+        <v>11996</v>
+      </c>
+      <c r="N8" s="1">
+        <v>14777</v>
+      </c>
+      <c r="O8" s="1">
+        <v>18221</v>
+      </c>
+      <c r="P8" s="1">
+        <v>18334</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>20433</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -682,8 +3333,44 @@
       <c r="E9" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F9" s="1">
+        <v>19996</v>
+      </c>
+      <c r="G9" s="1">
+        <v>27964</v>
+      </c>
+      <c r="H9" s="1">
+        <v>27444</v>
+      </c>
+      <c r="I9" s="1">
+        <v>8879</v>
+      </c>
+      <c r="J9" s="1">
+        <v>4766</v>
+      </c>
+      <c r="K9" s="1">
+        <v>3890</v>
+      </c>
+      <c r="L9" s="1">
+        <v>5502</v>
+      </c>
+      <c r="M9" s="1">
+        <v>5771</v>
+      </c>
+      <c r="N9" s="1">
+        <v>8724</v>
+      </c>
+      <c r="O9" s="1">
+        <v>10465</v>
+      </c>
+      <c r="P9" s="1">
+        <v>11795</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>20336</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -699,8 +3386,44 @@
       <c r="E10" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F10" s="1">
+        <v>4353</v>
+      </c>
+      <c r="G10" s="1">
+        <v>16058</v>
+      </c>
+      <c r="H10" s="1">
+        <v>14046</v>
+      </c>
+      <c r="I10" s="1">
+        <v>8368</v>
+      </c>
+      <c r="J10" s="1">
+        <v>6683</v>
+      </c>
+      <c r="K10" s="1">
+        <v>6029</v>
+      </c>
+      <c r="L10" s="1">
+        <v>7417</v>
+      </c>
+      <c r="M10" s="1">
+        <v>7928</v>
+      </c>
+      <c r="N10" s="1">
+        <v>10146</v>
+      </c>
+      <c r="O10" s="1">
+        <v>10618</v>
+      </c>
+      <c r="P10" s="1">
+        <v>10217</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>11076</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -716,8 +3439,44 @@
       <c r="E11" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F11" s="1">
+        <v>13813</v>
+      </c>
+      <c r="G11" s="1">
+        <v>18186</v>
+      </c>
+      <c r="H11" s="1">
+        <v>17999</v>
+      </c>
+      <c r="I11" s="1">
+        <v>6229</v>
+      </c>
+      <c r="J11" s="1">
+        <v>3204</v>
+      </c>
+      <c r="K11" s="1">
+        <v>2404</v>
+      </c>
+      <c r="L11" s="1">
+        <v>3534</v>
+      </c>
+      <c r="M11" s="1">
+        <v>4100</v>
+      </c>
+      <c r="N11" s="1">
+        <v>6610</v>
+      </c>
+      <c r="O11" s="1">
+        <v>6770</v>
+      </c>
+      <c r="P11" s="1">
+        <v>7279</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>13754</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -733,8 +3492,44 @@
       <c r="E12" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F12" s="1">
+        <v>6152</v>
+      </c>
+      <c r="G12" s="1">
+        <v>13797</v>
+      </c>
+      <c r="H12" s="1">
+        <v>11189</v>
+      </c>
+      <c r="I12" s="1">
+        <v>4649</v>
+      </c>
+      <c r="J12" s="1">
+        <v>3820</v>
+      </c>
+      <c r="K12" s="1">
+        <v>3712</v>
+      </c>
+      <c r="L12" s="1">
+        <v>4336</v>
+      </c>
+      <c r="M12" s="1">
+        <v>5558</v>
+      </c>
+      <c r="N12" s="1">
+        <v>6725</v>
+      </c>
+      <c r="O12" s="1">
+        <v>8145</v>
+      </c>
+      <c r="P12" s="1">
+        <v>8610</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>9531</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -750,8 +3545,44 @@
       <c r="E13" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F13" s="1">
+        <v>5244</v>
+      </c>
+      <c r="G13" s="1">
+        <v>10975</v>
+      </c>
+      <c r="H13" s="1">
+        <v>9792</v>
+      </c>
+      <c r="I13" s="1">
+        <v>5153</v>
+      </c>
+      <c r="J13" s="1">
+        <v>4531</v>
+      </c>
+      <c r="K13" s="1">
+        <v>4304</v>
+      </c>
+      <c r="L13" s="1">
+        <v>4957</v>
+      </c>
+      <c r="M13" s="1">
+        <v>5326</v>
+      </c>
+      <c r="N13" s="1">
+        <v>6221</v>
+      </c>
+      <c r="O13" s="1">
+        <v>7064</v>
+      </c>
+      <c r="P13" s="1">
+        <v>7677</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>10388</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -767,8 +3598,44 @@
       <c r="E14" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F14" s="1">
+        <v>3504</v>
+      </c>
+      <c r="G14" s="1">
+        <v>6587</v>
+      </c>
+      <c r="H14" s="1">
+        <v>5862</v>
+      </c>
+      <c r="I14" s="1">
+        <v>2924</v>
+      </c>
+      <c r="J14" s="1">
+        <v>2624</v>
+      </c>
+      <c r="K14" s="1">
+        <v>2822</v>
+      </c>
+      <c r="L14" s="1">
+        <v>4094</v>
+      </c>
+      <c r="M14" s="1">
+        <v>4257</v>
+      </c>
+      <c r="N14" s="1">
+        <v>4357</v>
+      </c>
+      <c r="O14" s="1">
+        <v>5914</v>
+      </c>
+      <c r="P14" s="1">
+        <v>5571</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>6946</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -784,8 +3651,44 @@
       <c r="E15" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F15" s="1">
+        <v>5429</v>
+      </c>
+      <c r="G15" s="1">
+        <v>6911</v>
+      </c>
+      <c r="H15" s="1">
+        <v>5078</v>
+      </c>
+      <c r="I15" s="1">
+        <v>2513</v>
+      </c>
+      <c r="J15" s="1">
+        <v>1932</v>
+      </c>
+      <c r="K15" s="1">
+        <v>2216</v>
+      </c>
+      <c r="L15" s="1">
+        <v>2962</v>
+      </c>
+      <c r="M15" s="1">
+        <v>2925</v>
+      </c>
+      <c r="N15" s="1">
+        <v>3483</v>
+      </c>
+      <c r="O15" s="1">
+        <v>3206</v>
+      </c>
+      <c r="P15" s="1">
+        <v>3731</v>
+      </c>
+      <c r="Q15" s="1">
+        <v>5547</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -801,8 +3704,44 @@
       <c r="E16" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F16" s="1">
+        <v>3136</v>
+      </c>
+      <c r="G16" s="1">
+        <v>5681</v>
+      </c>
+      <c r="H16" s="1">
+        <v>5068</v>
+      </c>
+      <c r="I16" s="1">
+        <v>2330</v>
+      </c>
+      <c r="J16" s="1">
+        <v>2149</v>
+      </c>
+      <c r="K16" s="1">
+        <v>2111</v>
+      </c>
+      <c r="L16" s="1">
+        <v>2889</v>
+      </c>
+      <c r="M16" s="1">
+        <v>3736</v>
+      </c>
+      <c r="N16" s="1">
+        <v>3632</v>
+      </c>
+      <c r="O16" s="1">
+        <v>4556</v>
+      </c>
+      <c r="P16" s="1">
+        <v>4649</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>5707</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -818,8 +3757,44 @@
       <c r="E17" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F17" s="1">
+        <v>4094</v>
+      </c>
+      <c r="G17" s="1">
+        <v>6508</v>
+      </c>
+      <c r="H17" s="1">
+        <v>5275</v>
+      </c>
+      <c r="I17" s="1">
+        <v>2086</v>
+      </c>
+      <c r="J17" s="1">
+        <v>1665</v>
+      </c>
+      <c r="K17" s="1">
+        <v>1488</v>
+      </c>
+      <c r="L17" s="1">
+        <v>2163</v>
+      </c>
+      <c r="M17" s="1">
+        <v>2399</v>
+      </c>
+      <c r="N17" s="1">
+        <v>2620</v>
+      </c>
+      <c r="O17" s="1">
+        <v>3797</v>
+      </c>
+      <c r="P17" s="1">
+        <v>3733</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>5012</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -835,8 +3810,44 @@
       <c r="E18" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F18" s="1">
+        <v>1462</v>
+      </c>
+      <c r="G18" s="1">
+        <v>3487</v>
+      </c>
+      <c r="H18" s="1">
+        <v>2164</v>
+      </c>
+      <c r="I18">
+        <v>872</v>
+      </c>
+      <c r="J18">
+        <v>824</v>
+      </c>
+      <c r="K18">
+        <v>742</v>
+      </c>
+      <c r="L18">
+        <v>867</v>
+      </c>
+      <c r="M18" s="1">
+        <v>1032</v>
+      </c>
+      <c r="N18" s="1">
+        <v>1357</v>
+      </c>
+      <c r="O18" s="1">
+        <v>1548</v>
+      </c>
+      <c r="P18" s="1">
+        <v>1760</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>2136</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -852,8 +3863,44 @@
       <c r="E19" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F19">
+        <v>633</v>
+      </c>
+      <c r="G19" s="1">
+        <v>1558</v>
+      </c>
+      <c r="H19" s="1">
+        <v>1151</v>
+      </c>
+      <c r="I19">
+        <v>405</v>
+      </c>
+      <c r="J19">
+        <v>336</v>
+      </c>
+      <c r="K19">
+        <v>496</v>
+      </c>
+      <c r="L19">
+        <v>597</v>
+      </c>
+      <c r="M19">
+        <v>632</v>
+      </c>
+      <c r="N19">
+        <v>555</v>
+      </c>
+      <c r="O19">
+        <v>704</v>
+      </c>
+      <c r="P19">
+        <v>717</v>
+      </c>
+      <c r="Q19">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -869,8 +3916,44 @@
       <c r="E20" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F20">
+        <v>674</v>
+      </c>
+      <c r="G20">
+        <v>913</v>
+      </c>
+      <c r="H20">
+        <v>851</v>
+      </c>
+      <c r="I20">
+        <v>361</v>
+      </c>
+      <c r="J20">
+        <v>249</v>
+      </c>
+      <c r="K20">
+        <v>271</v>
+      </c>
+      <c r="L20">
+        <v>599</v>
+      </c>
+      <c r="M20">
+        <v>708</v>
+      </c>
+      <c r="N20">
+        <v>661</v>
+      </c>
+      <c r="O20">
+        <v>722</v>
+      </c>
+      <c r="P20">
+        <v>685</v>
+      </c>
+      <c r="Q20">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -885,19 +3968,46 @@
       </c>
       <c r="E21" t="s">
         <v>35</v>
+      </c>
+      <c r="F21">
+        <v>249</v>
+      </c>
+      <c r="G21">
+        <v>648</v>
+      </c>
+      <c r="H21">
+        <v>650</v>
+      </c>
+      <c r="I21">
+        <v>265</v>
+      </c>
+      <c r="J21">
+        <v>370</v>
+      </c>
+      <c r="K21">
+        <v>224</v>
+      </c>
+      <c r="L21">
+        <v>287</v>
+      </c>
+      <c r="M21">
+        <v>312</v>
+      </c>
+      <c r="N21">
+        <v>355</v>
+      </c>
+      <c r="O21">
+        <v>427</v>
+      </c>
+      <c r="P21">
+        <v>418</v>
+      </c>
+      <c r="Q21">
+        <v>609</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73C37A12-E6F8-4DDA-A21F-87BDE073DC18}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-</worksheet>
 </file>